--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-observation-microbiology.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1053,7 +1053,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>【JP Core仕様】[Slicing](http://hl7.org/fhir/R4/profiling.html#slicing)を使用して複数のコード体系に対応  
+    <t>【JP Core仕様】[Slicing](http://hl7.org/fhir/R4B/profiling.html#slicing)を使用して複数のコード体系に対応  
 基本方針としてカテゴリに応じた標準コードの使用を想定しているが、ローカルコードを使用してもよい</t>
   </si>
   <si>
